--- a/target/classes/Stores.xlsx
+++ b/target/classes/Stores.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
   <si>
     <t xml:space="preserve">UUID</t>
   </si>
@@ -28,10 +28,19 @@
     <t xml:space="preserve">name</t>
   </si>
   <si>
-    <t xml:space="preserve">$price[USD]</t>
-  </si>
-  <si>
-    <t xml:space="preserve">a</t>
+    <t xml:space="preserve">price</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A78gs6D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pepper</t>
+  </si>
+  <si>
+    <t xml:space="preserve">o0Ty8l1I</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chilli</t>
   </si>
 </sst>
 </file>
@@ -106,12 +115,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -238,7 +251,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -253,8 +266,25 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="s">
+      <c r="A2" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="0" t="n">
+        <v>6.99</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>5</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="0" t="n">
+        <v>7.99</v>
       </c>
     </row>
   </sheetData>
